--- a/volunteer_registration_forms/030_volunteer_work_week_registration_form--volunteer_registration_forms.xlsx
+++ b/volunteer_registration_forms/030_volunteer_work_week_registration_form--volunteer_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="39" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Description 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Description 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>assigned_tool_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>Assigned Tool 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>form_ids_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>Form Ids 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Description 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>Category 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>output_file_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>output_file</t>
+          <t>Output File 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>description_5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>description</t>
+          <t>Description 5</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>form_ids_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>form_ids</t>
+          <t>Form Ids 3</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1165,29 +1165,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>volunteer</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Volunteer</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>volunteer_type_choices</t>
+          <t>organization_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>non-profit_organization</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Non-profit Organization</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>non-profit_organization</t>
+          <t>community_group</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Non-profit Organization</t>
+          <t>Community Group</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>community_group</t>
+          <t>school</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Community Group</t>
+          <t>School</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>school</t>
+          <t>event_organizer</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>School</t>
+          <t>Event Organizer</t>
         </is>
       </c>
     </row>
@@ -1250,29 +1250,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>event_organizer</t>
+          <t>educational_institution</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Event Organizer</t>
+          <t>Educational Institution</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>organization_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>educational_institution</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Educational Institution</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>volunteer_registration_forms</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Volunteer Registration Forms</t>
         </is>
       </c>
     </row>
@@ -1318,29 +1318,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>volunteer_registration_forms</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Volunteer Registration Forms</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>output_file_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>030_volunteer_work_week_registration_form--volunteer_registration_forms</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>030 volunteer work week registration form--volunteer registration forms</t>
         </is>
       </c>
     </row>
@@ -1352,129 +1352,112 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>030_volunteer_work_week_registration_form--volunteer_registration_forms</t>
+          <t>031_volunteer_work_week_registration_form--volunteer_registration_forms</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>030_volunteer_work_week_registration_form--volunteer_registration_forms</t>
+          <t>031 volunteer work week registration form--volunteer registration forms</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>output_file_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>031_volunteer_work_week_registration_form--volunteer_registration_forms</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>031_volunteer_work_week_registration_form--volunteer_registration_forms</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>assigned_tool_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>assigned_tool_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>volunteer_registration_forms</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>Volunteer Registration Forms</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>category_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>volunteer_registration_forms</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Volunteer Registration Forms</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>category_choices</t>
+          <t>output_file_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>output_file_choices</t>
+          <t>output_file_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>output_file_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
